--- a/reports/jobs_2026-09-28.xlsx
+++ b/reports/jobs_2026-09-28.xlsx
@@ -520,12 +520,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Arm India</t>
+          <t>Agoda India</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Tools &amp; Licensing Applications Engineer</t>
+          <t>Business Intelligence Developer, RTA (Bangkok-based, 6-month Contract) Technology Bangkok, Thailand</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -538,11 +538,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>2026-09-28</t>
@@ -550,12 +546,12 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/job/bengaluru/tools-and-licensing-applications-engineer/33099/101252909856</t>
+          <t>https://careersatagoda.com/job/7100648-business-intelligence-developer-rta-bangkok-based-6-month-contract/</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/</t>
+          <t>https://careersatagoda.com/</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -567,17 +563,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Arm India</t>
+          <t>Thoughtworks India</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Digital Experience Strategist – Physical AI &amp; Developer Program</t>
+          <t>Software Procurement Intern</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -585,7 +581,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Bangalore, India; Gurgaon, India; Pune, India</t>
+        </is>
+      </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
           <t>2026-09-28</t>
@@ -593,12 +593,12 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/job/cambridge/digital-experience-strategist-physical-ai-and-developer-program/33099/101252904320</t>
+          <t>https://www.thoughtworks.com/careers/jobs/8236673?gh_jid=8236673</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/</t>
+          <t>https://boards.greenhouse.io/thoughtworks</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -1895,12 +1895,12 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>SME - Data Science &amp; AI expert</t>
+          <t>Gen AI Engineer</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Gurgaon/SME---Data-Science---AI-expert_SR-46203</t>
+          <t>https://fractal.ai/en-US/Careers/job/Mumbai/Gen-AI-Engineer_SR-45659-1</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Engineering Leader, Google COE</t>
+          <t>SME - Data Science &amp; AI expert</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/California/Principal-Consultant-Decision-Scientist-4_SR-42734-1</t>
+          <t>https://fractal.ai/en-US/Careers/job/Gurgaon/SME---Data-Science---AI-expert_SR-46203</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -1976,12 +1976,12 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>GitLab India</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Software composition analysis</t>
+          <t>Engineering Leader, Google COE</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -2002,12 +2002,12 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/solutions/supply-chain/</t>
+          <t>https://fractal.ai/en-US/Careers/job/California/Principal-Consultant-Decision-Scientist-4_SR-42734-1</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/jobs/all-jobs/</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
@@ -2019,17 +2019,17 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>GitLab India</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Internships and Programs</t>
+          <t>Software composition analysis</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -2045,12 +2045,12 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
+          <t>https://about.gitlab.com/solutions/supply-chain/</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://about.gitlab.com/jobs/all-jobs/</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
@@ -2067,12 +2067,12 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
+          <t>Internships and Programs</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
+          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -2105,17 +2105,17 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -2123,11 +2123,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru-VTP, India</t>
-        </is>
-      </c>
+      <c r="E37" s="4" t="inlineStr"/>
       <c r="F37" s="4" t="inlineStr">
         <is>
           <t>2026-09-28</t>
@@ -2135,12 +2131,12 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
+          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/groww</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
@@ -2157,7 +2153,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>YouTube &amp; Content - Internship</t>
+          <t>Video Editor Intern</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -2182,7 +2178,7 @@
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4967486101</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -2199,17 +2195,17 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>HighRadius</t>
+          <t>Groww</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>YouTube &amp; Content - Internship</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -2219,7 +2215,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>Bengaluru-VTP, India</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -2229,12 +2225,12 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4967486101</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/highradius</t>
+          <t>https://boards.greenhouse.io/groww</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
@@ -2246,12 +2242,12 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Ixigo</t>
+          <t>HighRadius</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -2266,7 +2262,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>New Delhi, in</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -2276,12 +2272,12 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
+          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/ixigo</t>
+          <t>https://boards.greenhouse.io/highradius</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
@@ -2293,17 +2289,17 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Lendingkart</t>
+          <t>Ixigo</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -2313,7 +2309,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru, in</t>
+          <t>New Delhi, in</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -2323,12 +2319,12 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/lendingkart</t>
+          <t>https://careers.smartrecruiters.com/ixigo</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
@@ -2340,17 +2336,17 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>Lendingkart</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Internship Opportunities</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -2358,7 +2354,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr"/>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
           <t>2026-09-28</t>
@@ -2366,12 +2366,12 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/pathways-programs/internships</t>
+          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://careers.smartrecruiters.com/lendingkart</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Internship Opportunities</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/Teams/Engineering</t>
+          <t>https://careers.linkedin.com/pathways-programs/internships</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -2426,12 +2426,12 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Meesho</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Cluster Head- Last mile - Chennai</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -2444,11 +2444,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>Chennai, Tamil Nadu</t>
-        </is>
-      </c>
+      <c r="E44" s="4" t="inlineStr"/>
       <c r="F44" s="4" t="inlineStr">
         <is>
           <t>2026-09-28</t>
@@ -2456,12 +2452,12 @@
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/c84e4b2c-653a-4cf8-abd9-e70d0c5e4cd8</t>
+          <t>https://careers.linkedin.com/Teams/Engineering</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
@@ -2478,7 +2474,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Trainee - Recruitment Coordinator</t>
+          <t>Cluster Head- Last mile - Chennai</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -2493,7 +2489,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Chennai, Tamil Nadu</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -2503,7 +2499,7 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/1de2fc88-e203-4f1a-8046-55df700de4be</t>
+          <t>https://jobs.lever.co/meesho/c84e4b2c-653a-4cf8-abd9-e70d0c5e4cd8</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
@@ -2520,12 +2516,12 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>MoEngage</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>For Developers</t>
+          <t>Trainee - Recruitment Coordinator</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -2538,7 +2534,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr"/>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
           <t>2026-09-28</t>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/role/for-developers/</t>
+          <t>https://jobs.lever.co/meesho/1de2fc88-e203-4f1a-8046-55df700de4be</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/careers/</t>
+          <t>https://jobs.lever.co/meesho</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
@@ -2563,12 +2563,12 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>MongoDB India</t>
+          <t>MoEngage</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Engineer 3 - Business Systems</t>
+          <t>For Developers</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -2581,11 +2581,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram</t>
-        </is>
-      </c>
+      <c r="E47" s="4" t="inlineStr"/>
       <c r="F47" s="4" t="inlineStr">
         <is>
           <t>2026-09-28</t>
@@ -2593,12 +2589,12 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=8122751</t>
+          <t>https://www.moengage.com/role/for-developers/</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/mongodb</t>
+          <t>https://www.moengage.com/careers/</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
@@ -2615,7 +2611,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer 3</t>
+          <t>Engineer 3 - Business Systems</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -2640,7 +2636,7 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=8167389</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=8122751</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -3999,19 +3995,19 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>Capillary Technologies</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://blinkit.com/careers</t>
+          <t>https://www.capillarytech.com/careers/</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
-  - navigating to "https://blinkit.com/careers", waiting until "networkidle"
+  - navigating to "https://www.capillarytech.com/careers/", waiting until "networkidle"
 </t>
         </is>
       </c>
@@ -4039,55 +4035,15 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Capillary Technologies</t>
+          <t>Nykaa</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://www.capillarytech.com/careers/</t>
+          <t>https://www.nykaa.com/careers</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.capillarytech.com/careers/", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Darwinbox</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>https://darwinbox.com/careers</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://darwinbox.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Nykaa</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>https://www.nykaa.com/careers</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.nykaa.com/careers
 Call log:
@@ -4096,18 +4052,18 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Juspay</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>https://juspay.io/careers</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4116,18 +4072,38 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FirstCry</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://www.firstcry.com/careers</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.firstcry.com/careers", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>MakeMyTrip</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>https://careers.makemytrip.com/</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4136,38 +4112,18 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>FirstCry</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>https://www.firstcry.com/careers</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.firstcry.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Pocket FM</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>https://pocketfm.com/careers</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4176,18 +4132,18 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Zomato</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>https://www.zomato.com/careers</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.zomato.com/careers
 Call log:
@@ -4196,6 +4152,46 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Shiprocket</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>https://www.shiprocket.in/careers/</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.shiprocket.in/careers/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Tata 1mg</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>https://www.1mg.com/jobs</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.1mg.com/jobs", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
